--- a/samples/ai-report/ai-report-check.xlsx
+++ b/samples/ai-report/ai-report-check.xlsx
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Какой статус заказа считается продажей в отчётном периоде?</t>
+          <t>Which order status counts as a sale in the period?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Как считать отменённые заказы?</t>
+          <t>How are cancelled orders counted?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Как распознаются и куда деваются тестовые и внутренние заказы?</t>
+          <t>How are test and internal orders recognised, and where do they go?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Что такое одна строка популяции: заказ или строка заказа?</t>
+          <t>Is one row of the population an order or an order line?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Чьи продажи входят в отчёт: собственные, продавцов площадки или обе группы?</t>
+          <t>Whose sales are in the report: the shop's own, marketplace sellers', or both?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>На какой базе считается ставка возвратов?</t>
+          <t>What is the refund rate taken over?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Как считается частичный возврат?</t>
+          <t>How is a partial refund counted?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>К какому периоду относится возврат: к периоду заказа или к периоду возврата?</t>
+          <t>Which period does a refund belong to: the order's or the refund's?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Что входит в сумму возврата: только товар, или и доставка, и комиссии?</t>
+          <t>What does a refund amount include: the goods only, or shipping and fees too?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Какая дата определяет принадлежность заказа периоду?</t>
+          <t>Which date puts an order in a period?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Границы периода включительные с обеих сторон или конец исключён?</t>
+          <t>Are the period's bounds inclusive at both ends, or is the end excluded?</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>В каком часовом поясе читается дата события?</t>
+          <t>In which time zone is an event's date read?</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Как читается строка заказа, у которой несколько версий в выгрузке?</t>
+          <t>How is an order line read when the export holds several versions of it?</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Что такое выручка в заголовке: до или после возвратов?</t>
+          <t>Is the headline revenue before or after refunds?</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Суммы в выручке с НДС или без?</t>
+          <t>Are revenue amounts with VAT or without?</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Сумма заказа берётся до или после скидок и промокодов?</t>
+          <t>Is an order's amount taken before or after discounts and codes?</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Плата за доставку входит в выручку?</t>
+          <t>Is the shipping fee revenue?</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>В какой валюте и по какому курсу суммируются заказы в разных валютах?</t>
+          <t>In which currency, and at which rate, are orders in different currencies added up?</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Где округляются суммы: по строке или в итоге?</t>
+          <t>Where are amounts rounded: per line or in the total?</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Что такое один клиент?</t>
+          <t>What is one customer?</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Как считать заказы без аккаунта (гостевые)?</t>
+          <t>How are orders without an account (guest checkouts) counted?</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Кто такой новый клиент периода?</t>
+          <t>Who is a new customer of the period?</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Кто такой платящий клиент в знаменателе ставок?</t>
+          <t>Who is a paying customer in the denominator of a rate?</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Что такое количество в строке: штуки, упаковки или вес?</t>
+          <t>What is the quantity on a line: pieces, packs or weight?</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Как считается набор (бандл) из нескольких товаров?</t>
+          <t>How is a bundle of several products counted?</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Что означает отрицательное количество или отрицательная сумма в строке?</t>
+          <t>What does a negative quantity or amount on a line mean?</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Как считать строки с нулевой суммой?</t>
+          <t>How are rows with a zero amount counted?</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Что такое канал заказа?</t>
+          <t>What is an order's channel?</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Как заказ относится к промокампании?</t>
+          <t>How is an order attributed to a promotion?</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Куда идут заказы с пустым или неизвестным каналом?</t>
+          <t>Where do orders with an empty or unknown channel go?</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Что делать с повторяющимся идентификатором заказа?</t>
+          <t>What is done with a repeated order id?</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Как поступать, если выгрузка не покрывает весь отчётный период?</t>
+          <t>What if the export does not cover the whole period?</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Как считать строки с пустой суммой?</t>
+          <t>How are rows with an empty amount counted?</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Что делать с колонками свободного текста (комментарии, адреса, заметки)?</t>
+          <t>What is done with free-text columns: comments, addresses, notes?</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5413,7 +5413,11 @@
           <t>product_sales_basis</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>What are a product's sales?</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>after_discounts_before_refunds</t>
@@ -5431,7 +5435,11 @@
           <t>discount_share_basis</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>What is the discount share taken over?</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>discounts_over_gross_sales</t>
@@ -5449,7 +5457,11 @@
           <t>repeat_customer_basis</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Who is a returning customer?</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>repeat_within_period</t>
@@ -5467,7 +5479,11 @@
           <t>aov_basis</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>What is the average order value?</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>net_sales_per_order</t>
@@ -5514,7 +5530,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected (Shopify's own record)</t>
+          <t>Expected (the order system's control file)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -5675,7 +5691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5704,39 +5720,53 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The export's control file is written by the generator: a Shopify export comes with no such file, and for a real shop the totals come from another source.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SHA-256</t>
+          <t>The 38 rules were answered by an AI model under the owner's delegation, not by the owner; 'Recorded as' on the rules sheet says so for each.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>orders_export.csv</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4655ea261d1446cdb828cbf2106dae16d141b625cdbf5ac543c048f57004881f</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>orders_export.csv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4655ea261d1446cdb828cbf2106dae16d141b625cdbf5ac543c048f57004881f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>report.md</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>af04d8493da5c7224bebb8b3f53698320103db82bada3bdfca013dcc07fbc58b</t>
         </is>
